--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.08605389737543</v>
+        <v>5.538983758323507</v>
       </c>
       <c r="D2" t="n">
-        <v>34.18631332338272</v>
+        <v>5.555275915049692</v>
       </c>
       <c r="E2" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F2" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.97128273168844</v>
+        <v>2.107833443899371</v>
       </c>
       <c r="D3" t="n">
-        <v>12.63761507452912</v>
+        <v>2.053612449610982</v>
       </c>
       <c r="E3" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F3" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.88524396616782</v>
+        <v>2.256352144502271</v>
       </c>
       <c r="D4" t="n">
-        <v>13.74430870098336</v>
+        <v>2.233450163909796</v>
       </c>
       <c r="E4" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F4" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.72169604739346</v>
+        <v>2.879775607701438</v>
       </c>
       <c r="D5" t="n">
-        <v>18.11139418677621</v>
+        <v>2.943101555351135</v>
       </c>
       <c r="E5" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F5" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.876936408468854</v>
+        <v>1.442502166376189</v>
       </c>
       <c r="D6" t="n">
-        <v>8.555216885248495</v>
+        <v>1.39022274385288</v>
       </c>
       <c r="E6" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F6" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.47125839009535</v>
+        <v>4.301579488390494</v>
       </c>
       <c r="D7" t="n">
-        <v>26.92419080290486</v>
+        <v>4.37518100547204</v>
       </c>
       <c r="E7" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F7" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.653726218599773</v>
+        <v>0.7562305105224632</v>
       </c>
       <c r="D8" t="n">
-        <v>13.6727220791584</v>
+        <v>2.221817337863241</v>
       </c>
       <c r="E8" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F8" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.93464435324226</v>
+        <v>3.239379707401867</v>
       </c>
       <c r="D9" t="n">
-        <v>19.92585704604634</v>
+        <v>3.237951769982531</v>
       </c>
       <c r="E9" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F9" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.23204331199508</v>
+        <v>5.887707038199202</v>
       </c>
       <c r="D10" t="n">
-        <v>36.33563521216107</v>
+        <v>5.904540721976175</v>
       </c>
       <c r="E10" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F10" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.43973139288498</v>
+        <v>3.808956351343809</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27010131886052</v>
+        <v>3.781391464314835</v>
       </c>
       <c r="E11" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F11" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.16453109484406</v>
+        <v>6.364236302912159</v>
       </c>
       <c r="D12" t="n">
-        <v>39.38961244075114</v>
+        <v>6.40081202162206</v>
       </c>
       <c r="E12" t="n">
-        <v>10.89813061732639</v>
+        <v>1.770946225315539</v>
       </c>
       <c r="F12" t="n">
-        <v>10.02525070208305</v>
+        <v>1.629103239088497</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
